--- a/Arquivos-Escopo/RegrasDeNegocio 1.xlsx
+++ b/Arquivos-Escopo/RegrasDeNegocio 1.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20384"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTG-2025\Desktop\AgroFlux2026\Arquivos-Escopo\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F30A8BB-7B75-481B-97B5-C7CF2805E28C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -22,107 +27,95 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
-    <t xml:space="preserve">REGRAS DE NEGÓCIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOME DA REGRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DESCRIÇÃO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RN 001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACESSO AO SISTEMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O USUÁRIO SÓ PODE ACESSAR O 
+    <t>REGRAS DE NEGÓCIO</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>NOME DA REGRA</t>
+  </si>
+  <si>
+    <t>DESCRIÇÃO</t>
+  </si>
+  <si>
+    <t>RN 001</t>
+  </si>
+  <si>
+    <t>ACESSO AO SISTEMA</t>
+  </si>
+  <si>
+    <t>O USUÁRIO SÓ PODE ACESSAR O 
 SISTEMA SE ESTIVER AUTENTICADO</t>
   </si>
   <si>
-    <t xml:space="preserve">RN 002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DADOS DUPLICADOS NÃO PODEM SER CADASTRADOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RN 003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O ESTOQUE DEVE SER ATUALIZADO AUTOMATICAMENTE APÓS ENTRADA OU SAÍDA DE PRODUTOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RN 004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O SISTEMA DEVE EMITIR ALERTA QUANDO O ESTOQUE ATINGIR NÍVEL MÍNIMO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RN 005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O SISTEMA NÃO DEVE PERMITIR A EXCLUSÃO DE PRODUTO QUE POSSUA QUANTIA EM ESTOQUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RN 006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APENAS USUÁRIOS COM PERFIL ADMINISTRADOR PODEM CADASTRAR OU EDITAR FUNCIONÁRIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RN 007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TODO FUNCIONÁRIO DEVE POSSUIR CPF VÁLIDO E ÚNICO</t>
+    <t>RN 002</t>
+  </si>
+  <si>
+    <t>DADOS DUPLICADOS NÃO PODEM SER CADASTRADOS</t>
+  </si>
+  <si>
+    <t>RN 003</t>
+  </si>
+  <si>
+    <t>O ESTOQUE DEVE SER ATUALIZADO AUTOMATICAMENTE APÓS ENTRADA OU SAÍDA DE PRODUTOS</t>
+  </si>
+  <si>
+    <t>RN 004</t>
+  </si>
+  <si>
+    <t>O SISTEMA DEVE EMITIR ALERTA QUANDO O ESTOQUE ATINGIR NÍVEL MÍNIMO</t>
+  </si>
+  <si>
+    <t>RN 005</t>
+  </si>
+  <si>
+    <t>O SISTEMA NÃO DEVE PERMITIR A EXCLUSÃO DE PRODUTO QUE POSSUA QUANTIA EM ESTOQUE</t>
+  </si>
+  <si>
+    <t>RN 006</t>
+  </si>
+  <si>
+    <t>APENAS USUÁRIOS COM PERFIL ADMINISTRADOR PODEM CADASTRAR OU EDITAR FUNCIONÁRIOS</t>
+  </si>
+  <si>
+    <t>RN 007</t>
+  </si>
+  <si>
+    <t>TODO FUNCIONÁRIO DEVE POSSUIR CPF VÁLIDO E ÚNICO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -154,126 +147,89 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="4">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8D281E"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFAFABAB"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCCCCC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -332,62 +288,78 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -440,29 +412,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:D10"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:H10"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="31.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.58"/>
+    <col min="3" max="3" width="31.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="2:8" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="2:8" ht="15.6" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
@@ -473,79 +444,85 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="2:8" ht="59.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="2:8" ht="42.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="2:8" ht="42.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4" t="s">
+      <c r="C6" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D6" s="7"/>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" spans="2:8" ht="42.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4" t="s">
+      <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" spans="2:8" ht="42.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D8" s="7"/>
+    </row>
+    <row r="9" spans="2:8" ht="42.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D9" s="7"/>
+    </row>
+    <row r="10" spans="2:8" ht="42.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="D10" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="7">
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="B2:D2"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPágina &amp;P</oddFooter>
   </headerFooter>

--- a/Arquivos-Escopo/RegrasDeNegocio 1.xlsx
+++ b/Arquivos-Escopo/RegrasDeNegocio 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTG-2025\Desktop\AgroFlux2026\Arquivos-Escopo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTG-2025\OneDrive - SESISENAISP - Escolas\Área de Trabalho\AgroFlux2026\Arquivos-Escopo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CD2128-706C-40DC-AEEA-DA3EE2374DF8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{D7CD2128-706C-40DC-AEEA-DA3EE2374DF8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{54335625-8650-4289-89F9-9B17E4F9629D}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>REGRAS DE NEGÓCIO</t>
   </si>
@@ -92,13 +92,23 @@
     <t xml:space="preserve">  O USUÁRIO SÓ PODE ACESSAR O SISTEMA SE ESTIVER AUTENTICADO</t>
   </si>
   <si>
-    <t>DADOS JA EXISTENTE</t>
-  </si>
-  <si>
     <t>ATUALIZAÇAO DE ESTOQUE</t>
   </si>
   <si>
     <t>ALERTA DE ESTOQUE BAIXO</t>
+  </si>
+  <si>
+    <t>DADOS JÁ EXISTENTE</t>
+  </si>
+  <si>
+    <t>EXCLUSÃO DE PRODUTOS</t>
+  </si>
+  <si>
+    <t>CADASTRO OU EDIÇÃO DE 
+USUÁRIO</t>
+  </si>
+  <si>
+    <t>CPF USUÁRIO</t>
   </si>
 </sst>
 </file>
@@ -184,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -194,9 +204,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -410,11 +417,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
     </row>
     <row r="3" spans="2:4" ht="15.6" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -431,7 +438,7 @@
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -443,9 +450,9 @@
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>17</v>
       </c>
     </row>
@@ -454,9 +461,9 @@
         <v>7</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -465,9 +472,9 @@
         <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -475,8 +482,10 @@
       <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="6" t="s">
+      <c r="C8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -484,8 +493,10 @@
       <c r="B9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="6" t="s">
+      <c r="C9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -493,8 +504,10 @@
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="6" t="s">
+      <c r="C10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>16</v>
       </c>
     </row>

--- a/Arquivos-Escopo/RegrasDeNegocio 1.xlsx
+++ b/Arquivos-Escopo/RegrasDeNegocio 1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTG-2025\OneDrive - SESISENAISP - Escolas\Área de Trabalho\AgroFlux2026\Arquivos-Escopo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTG-2025\Desktop\AgroFlux2026\Arquivos-Escopo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{D7CD2128-706C-40DC-AEEA-DA3EE2374DF8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{54335625-8650-4289-89F9-9B17E4F9629D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEA6F09-87DE-4DBF-A62D-23D223CA3EAA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -85,10 +85,6 @@
  POSSUIR CPF VÁLIDO E ÚNICO</t>
   </si>
   <si>
-    <t xml:space="preserve">     DADOS DUPLICADOS NÃO
-       PODEM SER CADASTRADOS</t>
-  </si>
-  <si>
     <t xml:space="preserve">  O USUÁRIO SÓ PODE ACESSAR O SISTEMA SE ESTIVER AUTENTICADO</t>
   </si>
   <si>
@@ -109,6 +105,10 @@
   </si>
   <si>
     <t>CPF USUÁRIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     DADOS DUPLICADOS NÃO
+       PODEM SER CADASTRADOS(COMO POR EXEMPLO PODUTOS QUE JÁ FORAM ANTES CADASTRADOS, OU NO CASO DE FÚNCIONARIOS, EMAIL QUE JÁ ESTEJA SENDO UTILIZADO)</t>
   </si>
 </sst>
 </file>
@@ -442,18 +442,18 @@
         <v>5</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="47.4" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="151.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="75" customHeight="1" x14ac:dyDescent="0.25">
@@ -461,7 +461,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>12</v>
@@ -472,7 +472,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>13</v>
@@ -483,7 +483,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>14</v>
@@ -494,7 +494,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>15</v>
@@ -505,7 +505,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>16</v>
